--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/pre LAM_HRM-2031-0240/Panel 02/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/pre LAM_HRM-2031-0240/Panel 02/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Front_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,15 +434,25 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Radius</t>
+          <t>Outer Radius</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>Inner Radius</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Diameter</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>Dimple</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Bump</t>
         </is>
@@ -460,22 +470,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.60443</v>
+        <v>17.63357</v>
       </c>
       <c r="D2" t="n">
-        <v>17.46036</v>
+        <v>17.23439</v>
       </c>
       <c r="E2" t="n">
-        <v>17.43631</v>
+        <v>17.49927</v>
       </c>
       <c r="F2" t="n">
-        <v>44.54067</v>
+        <v>59.46644</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05224</v>
+        <v>43.58739</v>
       </c>
       <c r="H2" t="n">
-        <v>1.91991</v>
+        <v>90.08797</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.05288</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.92283</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +501,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.65569</v>
+        <v>17.60617</v>
       </c>
       <c r="D3" t="n">
-        <v>16.82421</v>
+        <v>17.41752</v>
       </c>
       <c r="E3" t="n">
-        <v>17.79928</v>
+        <v>17.47327</v>
       </c>
       <c r="F3" t="n">
-        <v>44.3426</v>
+        <v>57.68882</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05347</v>
+        <v>44.46253</v>
       </c>
       <c r="H3" t="n">
-        <v>1.95729</v>
+        <v>89.67498000000001</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.05291</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.89866</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +532,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.63025</v>
+        <v>18.0118</v>
       </c>
       <c r="D4" t="n">
-        <v>17.47569</v>
+        <v>17.19045</v>
       </c>
       <c r="E4" t="n">
-        <v>17.47741</v>
+        <v>17.65824</v>
       </c>
       <c r="F4" t="n">
-        <v>44.3008</v>
+        <v>58.80224</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05239</v>
+        <v>45.57112</v>
       </c>
       <c r="H4" t="n">
-        <v>1.92443</v>
+        <v>89.02</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.05376</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.92019</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +563,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17.2817</v>
+        <v>17.75259</v>
       </c>
       <c r="D5" t="n">
-        <v>17.53384</v>
+        <v>17.60675</v>
       </c>
       <c r="E5" t="n">
-        <v>17.47655</v>
+        <v>17.63428</v>
       </c>
       <c r="F5" t="n">
-        <v>44.5379</v>
+        <v>58.19373</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05254</v>
+        <v>44.55248</v>
       </c>
       <c r="H5" t="n">
-        <v>1.85267</v>
+        <v>89.34350000000001</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.05296</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.94069</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +594,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.74598</v>
+        <v>17.68194</v>
       </c>
       <c r="D6" t="n">
-        <v>17.09335</v>
+        <v>17.11343</v>
       </c>
       <c r="E6" t="n">
-        <v>17.564</v>
+        <v>17.54306</v>
       </c>
       <c r="F6" t="n">
-        <v>44.94525</v>
+        <v>58.12538</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05285</v>
+        <v>43.36784</v>
       </c>
       <c r="H6" t="n">
-        <v>1.96598</v>
+        <v>90.41054</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.05289</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.90655</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +625,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.4752</v>
+        <v>17.47042</v>
       </c>
       <c r="D7" t="n">
-        <v>17.23371</v>
+        <v>17.23745</v>
       </c>
       <c r="E7" t="n">
-        <v>17.44951</v>
+        <v>17.43434</v>
       </c>
       <c r="F7" t="n">
-        <v>44.93023</v>
+        <v>58.98689</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05162</v>
+        <v>43.75773</v>
       </c>
       <c r="H7" t="n">
-        <v>1.92401</v>
+        <v>90.55674</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.05359</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.90175</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +656,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>18.00726</v>
+        <v>17.3411</v>
       </c>
       <c r="D8" t="n">
-        <v>17.20421</v>
+        <v>17.22111</v>
       </c>
       <c r="E8" t="n">
-        <v>17.34287</v>
+        <v>17.30824</v>
       </c>
       <c r="F8" t="n">
-        <v>43.92567</v>
+        <v>57.51101</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05269</v>
+        <v>44.26354</v>
       </c>
       <c r="H8" t="n">
-        <v>1.92224</v>
+        <v>88.75776999999999</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.05351</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.8733</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +687,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.46947</v>
+        <v>17.77547</v>
       </c>
       <c r="D9" t="n">
-        <v>17.32899</v>
+        <v>17.49071</v>
       </c>
       <c r="E9" t="n">
-        <v>17.24493</v>
+        <v>17.70203</v>
       </c>
       <c r="F9" t="n">
-        <v>45.05247</v>
+        <v>57.56346</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05284</v>
+        <v>44.8325</v>
       </c>
       <c r="H9" t="n">
-        <v>1.93533</v>
+        <v>87.33391</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.05328</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.91679</v>
       </c>
     </row>
     <row r="10">
@@ -660,712 +718,910 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.66862</v>
+        <v>17.7531</v>
       </c>
       <c r="D10" t="n">
-        <v>17.5647</v>
+        <v>16.99257</v>
       </c>
       <c r="E10" t="n">
-        <v>17.62787</v>
+        <v>17.49196</v>
       </c>
       <c r="F10" t="n">
-        <v>44.49469</v>
+        <v>57.02213</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05308</v>
+        <v>44.58895</v>
       </c>
       <c r="H10" t="n">
-        <v>1.91047</v>
+        <v>89.00367</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.05419</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.90234</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Pad 2</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>17.50149</v>
-      </c>
-      <c r="D11" t="n">
-        <v>17.37655</v>
-      </c>
-      <c r="E11" t="n">
-        <v>17.46408</v>
-      </c>
-      <c r="F11" t="n">
-        <v>44.52918</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.053</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1.87402</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Outer Radius</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Inner Radius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Diameter</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Pad 2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>18.1356</v>
+        <v>17.61692</v>
       </c>
       <c r="D12" t="n">
-        <v>17.29782</v>
+        <v>17.23768</v>
       </c>
       <c r="E12" t="n">
-        <v>17.23884</v>
+        <v>17.34028</v>
       </c>
       <c r="F12" t="n">
-        <v>44.44296</v>
+        <v>57.79609</v>
       </c>
       <c r="G12" t="n">
-        <v>0.05226</v>
+        <v>43.45491</v>
       </c>
       <c r="H12" t="n">
-        <v>1.90159</v>
+        <v>89.37008</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.05311</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.93081</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>17.34386</v>
+        <v>17.54415</v>
       </c>
       <c r="D13" t="n">
-        <v>17.19206</v>
+        <v>17.16814</v>
       </c>
       <c r="E13" t="n">
-        <v>17.55874</v>
+        <v>17.3158</v>
       </c>
       <c r="F13" t="n">
-        <v>44.33027</v>
+        <v>59.59037</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05279</v>
+        <v>44.53235</v>
       </c>
       <c r="H13" t="n">
-        <v>1.88125</v>
+        <v>88.77719</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.05275</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.92965</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>17.46497</v>
+        <v>17.93613</v>
       </c>
       <c r="D14" t="n">
-        <v>17.26532</v>
+        <v>17.573</v>
       </c>
       <c r="E14" t="n">
-        <v>17.63574</v>
+        <v>17.60919</v>
       </c>
       <c r="F14" t="n">
-        <v>43.97157</v>
+        <v>57.66298</v>
       </c>
       <c r="G14" t="n">
-        <v>0.05323</v>
+        <v>44.02082</v>
       </c>
       <c r="H14" t="n">
-        <v>1.93565</v>
+        <v>88.94959</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.05251</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.92864</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17.62053</v>
+        <v>17.72597</v>
       </c>
       <c r="D15" t="n">
-        <v>17.33385</v>
+        <v>17.51776</v>
       </c>
       <c r="E15" t="n">
-        <v>17.57139</v>
+        <v>17.53709</v>
       </c>
       <c r="F15" t="n">
-        <v>44.51619</v>
+        <v>57.70839</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0521</v>
+        <v>45.08549</v>
       </c>
       <c r="H15" t="n">
-        <v>1.88741</v>
+        <v>89.28783</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.05195</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.90809</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17.29833</v>
+        <v>17.38939</v>
       </c>
       <c r="D16" t="n">
-        <v>17.27093</v>
+        <v>17.29107</v>
       </c>
       <c r="E16" t="n">
-        <v>17.76292</v>
+        <v>17.35836</v>
       </c>
       <c r="F16" t="n">
-        <v>43.70772</v>
+        <v>57.21038</v>
       </c>
       <c r="G16" t="n">
-        <v>0.05289</v>
+        <v>44.88047</v>
       </c>
       <c r="H16" t="n">
-        <v>1.88085</v>
+        <v>87.87584</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.05217</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.92361</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17.74751</v>
+        <v>17.44461</v>
       </c>
       <c r="D17" t="n">
-        <v>17.24032</v>
+        <v>16.9968</v>
       </c>
       <c r="E17" t="n">
-        <v>17.29796</v>
+        <v>17.35294</v>
       </c>
       <c r="F17" t="n">
-        <v>44.44798</v>
+        <v>58.32374</v>
       </c>
       <c r="G17" t="n">
-        <v>0.05342</v>
+        <v>44.46421</v>
       </c>
       <c r="H17" t="n">
-        <v>1.85839</v>
+        <v>88.80275</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.05284</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.94943</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>17.74429</v>
+        <v>17.68763</v>
       </c>
       <c r="D18" t="n">
-        <v>17.27174</v>
+        <v>17.13017</v>
       </c>
       <c r="E18" t="n">
-        <v>17.40841</v>
+        <v>17.3576</v>
       </c>
       <c r="F18" t="n">
-        <v>44.00761</v>
+        <v>57.91794</v>
       </c>
       <c r="G18" t="n">
-        <v>0.05288</v>
+        <v>44.32933</v>
       </c>
       <c r="H18" t="n">
-        <v>1.89038</v>
+        <v>88.21643</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.05302</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.93582</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>17.70347</v>
+      </c>
+      <c r="D19" t="n">
+        <v>17.24745</v>
+      </c>
+      <c r="E19" t="n">
+        <v>17.61869</v>
+      </c>
+      <c r="F19" t="n">
+        <v>57.63575</v>
+      </c>
+      <c r="G19" t="n">
+        <v>44.12688</v>
+      </c>
+      <c r="H19" t="n">
+        <v>89.3152</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.05305</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.92659</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>Unit 3</t>
         </is>
       </c>
-      <c r="C19" t="n">
-        <v>17.54935</v>
-      </c>
-      <c r="D19" t="n">
-        <v>17.35924</v>
-      </c>
-      <c r="E19" t="n">
-        <v>17.5881</v>
-      </c>
-      <c r="F19" t="n">
-        <v>43.76802</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.05261</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1.9385</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
+      <c r="C20" t="n">
+        <v>17.77416</v>
+      </c>
+      <c r="D20" t="n">
+        <v>17.04885</v>
+      </c>
+      <c r="E20" t="n">
+        <v>17.24252</v>
+      </c>
+      <c r="F20" t="n">
+        <v>57.87807</v>
+      </c>
+      <c r="G20" t="n">
+        <v>44.95181</v>
+      </c>
+      <c r="H20" t="n">
+        <v>90.53955000000001</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.05395</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.90604</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>via 1</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>0.63976</v>
-      </c>
-      <c r="D21" t="n">
-        <v>1.17923</v>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Trace 1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.63549</v>
+        <v>17.73016</v>
       </c>
       <c r="D22" t="n">
-        <v>1.15258</v>
+        <v>16.71816</v>
+      </c>
+      <c r="E22" t="n">
+        <v>16.87183</v>
+      </c>
+      <c r="F22" t="n">
+        <v>23.01011</v>
+      </c>
+      <c r="G22" t="n">
+        <v>35.05133</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.63692</v>
+        <v>17.2066</v>
       </c>
       <c r="D23" t="n">
-        <v>1.15786</v>
+        <v>16.59011</v>
+      </c>
+      <c r="E23" t="n">
+        <v>17.15031</v>
+      </c>
+      <c r="F23" t="n">
+        <v>22.74806</v>
+      </c>
+      <c r="G23" t="n">
+        <v>35.0143</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.64196</v>
+        <v>16.96114</v>
       </c>
       <c r="D24" t="n">
-        <v>1.16778</v>
+        <v>16.48377</v>
+      </c>
+      <c r="E24" t="n">
+        <v>16.85908</v>
+      </c>
+      <c r="F24" t="n">
+        <v>23.00367</v>
+      </c>
+      <c r="G24" t="n">
+        <v>36.03431</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.63465</v>
+        <v>17.18412</v>
       </c>
       <c r="D25" t="n">
-        <v>1.15755</v>
+        <v>16.69551</v>
+      </c>
+      <c r="E25" t="n">
+        <v>17.16997</v>
+      </c>
+      <c r="F25" t="n">
+        <v>22.93181</v>
+      </c>
+      <c r="G25" t="n">
+        <v>36.18047</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.63615</v>
+        <v>17.50724</v>
       </c>
       <c r="D26" t="n">
-        <v>1.15716</v>
+        <v>16.81714</v>
+      </c>
+      <c r="E26" t="n">
+        <v>16.91624</v>
+      </c>
+      <c r="F26" t="n">
+        <v>22.59531</v>
+      </c>
+      <c r="G26" t="n">
+        <v>36.20798</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.63231</v>
+        <v>17.31543</v>
       </c>
       <c r="D27" t="n">
-        <v>1.15344</v>
+        <v>16.66539</v>
+      </c>
+      <c r="E27" t="n">
+        <v>17.08466</v>
+      </c>
+      <c r="F27" t="n">
+        <v>22.69051</v>
+      </c>
+      <c r="G27" t="n">
+        <v>35.70266</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.63465</v>
+        <v>17.53441</v>
       </c>
       <c r="D28" t="n">
-        <v>1.17753</v>
+        <v>16.5029</v>
+      </c>
+      <c r="E28" t="n">
+        <v>17.15126</v>
+      </c>
+      <c r="F28" t="n">
+        <v>22.47502</v>
+      </c>
+      <c r="G28" t="n">
+        <v>35.87643</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>17.8631</v>
+      </c>
+      <c r="D29" t="n">
+        <v>16.75602</v>
+      </c>
+      <c r="E29" t="n">
+        <v>17.24742</v>
+      </c>
+      <c r="F29" t="n">
+        <v>22.72004</v>
+      </c>
+      <c r="G29" t="n">
+        <v>35.84464</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>Unit 3</t>
         </is>
       </c>
-      <c r="C29" t="n">
-        <v>0.62861</v>
-      </c>
-      <c r="D29" t="n">
-        <v>1.15324</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="C30" t="inlineStr">
+      <c r="C30" t="n">
+        <v>17.23978</v>
+      </c>
+      <c r="D30" t="n">
+        <v>16.85253</v>
+      </c>
+      <c r="E30" t="n">
+        <v>17.23026</v>
+      </c>
+      <c r="F30" t="n">
+        <v>22.05613</v>
+      </c>
+      <c r="G30" t="n">
+        <v>36.46155</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Rz max</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>Rz mean</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Rz min</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>Rz max</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>Ra mean</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>Ra Std dev</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>Ra min</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>Ra max</t>
         </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>roughness</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>0.7851</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0.08483</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0.64277</v>
-      </c>
-      <c r="F31" t="n">
-        <v>1.02072</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0.1151</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0.00793</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0.09793</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0.12986</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>roughness</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.77563</v>
+        <v>0.78127</v>
       </c>
       <c r="D32" t="n">
-        <v>0.08515</v>
+        <v>0.08555</v>
       </c>
       <c r="E32" t="n">
-        <v>0.64317</v>
+        <v>0.65243</v>
       </c>
       <c r="F32" t="n">
-        <v>1.02013</v>
+        <v>1.00896</v>
       </c>
       <c r="G32" t="n">
-        <v>0.11686</v>
+        <v>0.11508</v>
       </c>
       <c r="H32" t="n">
-        <v>0.00809</v>
+        <v>0.007939999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>0.09643</v>
+        <v>0.09704</v>
       </c>
       <c r="J32" t="n">
-        <v>0.13489</v>
+        <v>0.13097</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.78843</v>
+        <v>0.79115</v>
       </c>
       <c r="D33" t="n">
-        <v>0.08445</v>
+        <v>0.08329</v>
       </c>
       <c r="E33" t="n">
-        <v>0.6281099999999999</v>
+        <v>0.6414800000000001</v>
       </c>
       <c r="F33" t="n">
-        <v>1.00694</v>
+        <v>1.00623</v>
       </c>
       <c r="G33" t="n">
-        <v>0.11202</v>
+        <v>0.11453</v>
       </c>
       <c r="H33" t="n">
-        <v>0.00781</v>
+        <v>0.00788</v>
       </c>
       <c r="I33" t="n">
-        <v>0.09453</v>
+        <v>0.09469</v>
       </c>
       <c r="J33" t="n">
-        <v>0.13043</v>
+        <v>0.13363</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.78416</v>
+        <v>0.77129</v>
       </c>
       <c r="D34" t="n">
-        <v>0.08436</v>
+        <v>0.08516</v>
       </c>
       <c r="E34" t="n">
-        <v>0.63284</v>
+        <v>0.64208</v>
       </c>
       <c r="F34" t="n">
-        <v>1.02982</v>
+        <v>1.00418</v>
       </c>
       <c r="G34" t="n">
-        <v>0.11409</v>
+        <v>0.11796</v>
       </c>
       <c r="H34" t="n">
-        <v>0.007849999999999999</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>0.09769</v>
+        <v>0.09668</v>
       </c>
       <c r="J34" t="n">
-        <v>0.13009</v>
+        <v>0.13219</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.77804</v>
+        <v>0.7916299999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>0.08494</v>
+        <v>0.08259</v>
       </c>
       <c r="E35" t="n">
-        <v>0.62939</v>
+        <v>0.64134</v>
       </c>
       <c r="F35" t="n">
-        <v>0.99916</v>
+        <v>1.03054</v>
       </c>
       <c r="G35" t="n">
-        <v>0.1131</v>
+        <v>0.1133</v>
       </c>
       <c r="H35" t="n">
-        <v>0.008</v>
+        <v>0.00788</v>
       </c>
       <c r="I35" t="n">
-        <v>0.097</v>
+        <v>0.09622</v>
       </c>
       <c r="J35" t="n">
-        <v>0.1324</v>
+        <v>0.13172</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.79251</v>
+        <v>0.79025</v>
       </c>
       <c r="D36" t="n">
-        <v>0.08654000000000001</v>
+        <v>0.08419</v>
       </c>
       <c r="E36" t="n">
-        <v>0.64363</v>
+        <v>0.6339900000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>0.99136</v>
+        <v>0.9928900000000001</v>
       </c>
       <c r="G36" t="n">
-        <v>0.113</v>
+        <v>0.11585</v>
       </c>
       <c r="H36" t="n">
-        <v>0.008059999999999999</v>
+        <v>0.00793</v>
       </c>
       <c r="I36" t="n">
-        <v>0.09737</v>
+        <v>0.09891999999999999</v>
       </c>
       <c r="J36" t="n">
-        <v>0.13247</v>
+        <v>0.13305</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.76867</v>
+        <v>0.79255</v>
       </c>
       <c r="D37" t="n">
-        <v>0.08457000000000001</v>
+        <v>0.08547</v>
       </c>
       <c r="E37" t="n">
-        <v>0.64352</v>
+        <v>0.63564</v>
       </c>
       <c r="F37" t="n">
-        <v>1.00827</v>
+        <v>1.00857</v>
       </c>
       <c r="G37" t="n">
-        <v>0.1152</v>
+        <v>0.11463</v>
       </c>
       <c r="H37" t="n">
-        <v>0.00796</v>
+        <v>0.00791</v>
       </c>
       <c r="I37" t="n">
-        <v>0.09669</v>
+        <v>0.09748</v>
       </c>
       <c r="J37" t="n">
-        <v>0.13216</v>
+        <v>0.1323</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.8032899999999999</v>
+        <v>0.78456</v>
       </c>
       <c r="D38" t="n">
-        <v>0.08467</v>
+        <v>0.0848</v>
       </c>
       <c r="E38" t="n">
-        <v>0.63736</v>
+        <v>0.6246699999999999</v>
       </c>
       <c r="F38" t="n">
-        <v>1.0014</v>
+        <v>1.03788</v>
       </c>
       <c r="G38" t="n">
-        <v>0.11485</v>
+        <v>0.11391</v>
       </c>
       <c r="H38" t="n">
-        <v>0.007849999999999999</v>
+        <v>0.00784</v>
       </c>
       <c r="I38" t="n">
-        <v>0.09622</v>
+        <v>0.09735000000000001</v>
       </c>
       <c r="J38" t="n">
-        <v>0.12996</v>
+        <v>0.13065</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.78176</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.08358</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.62898</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.01096</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.11399</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.00792</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.09615</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.13151</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>Unit 3</t>
         </is>
       </c>
-      <c r="C39" t="n">
-        <v>0.77955</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0.08552999999999999</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0.61505</v>
-      </c>
-      <c r="F39" t="n">
-        <v>1.0241</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0.11405</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0.007990000000000001</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0.09764</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0.13102</v>
+      <c r="C40" t="n">
+        <v>0.77904</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.08551</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.62817</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.01139</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.11614</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.00796</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.09723999999999999</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.13312</v>
       </c>
     </row>
   </sheetData>
